--- a/lab1/Results_lab1_p2.xlsx
+++ b/lab1/Results_lab1_p2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chern\python\MPiAA\Lab1\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chern\python\MPiAA\Lab1\lab1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F585BF5-9525-4FE7-B939-218A1826849F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50F0A407-124A-48B4-A978-606F5A6F4038}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="12156" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="15">
   <si>
     <t>Время</t>
   </si>
@@ -64,33 +64,6 @@
   </si>
   <si>
     <t>O(n)</t>
-  </si>
-  <si>
-    <t>Сложность</t>
-  </si>
-  <si>
-    <r>
-      <t>Лучшая: O(1)       Худшая: O(n</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-      </rPr>
-      <t>²</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16.100000000000001"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>)</t>
-    </r>
   </si>
   <si>
     <r>
@@ -115,6 +88,9 @@
       </rPr>
       <t>)</t>
     </r>
+  </si>
+  <si>
+    <t>Теоретическая временная сложность</t>
   </si>
 </sst>
 </file>
@@ -185,10 +161,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -205,99 +181,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>209550</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>28575</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>171785</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>57353</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="9" name="Рисунок 8">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2E5BBF53-A63C-A06D-6339-65040E8C7E78}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="10353675" y="2409825"/>
-          <a:ext cx="2400635" cy="1457528"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>161925</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>209550</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>362318</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>19256</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="10" name="Рисунок 9">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D25D9E50-D38E-A421-CB7D-C09B111925B2}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="10658475" y="447675"/>
-          <a:ext cx="2638793" cy="1476581"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -569,34 +452,34 @@
     <col min="1" max="1" width="38" style="2" customWidth="1"/>
     <col min="2" max="2" width="25.33203125" style="2" customWidth="1"/>
     <col min="3" max="3" width="32.6640625" style="2" customWidth="1"/>
-    <col min="4" max="4" width="26.88671875" style="2" customWidth="1"/>
+    <col min="4" max="4" width="44.6640625" style="2" customWidth="1"/>
     <col min="5" max="16384" width="9.109375" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="3" t="s">
-        <v>13</v>
+      <c r="D1" s="4" t="s">
+        <v>14</v>
       </c>
       <c r="E1" s="1"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A2" s="3"/>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
+      <c r="A2" s="4"/>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
       <c r="E2" s="1"/>
     </row>
     <row r="3" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="3" t="s">
         <v>5</v>
       </c>
       <c r="B3" s="1">
@@ -605,50 +488,50 @@
       <c r="C3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="4" t="s">
         <v>12</v>
       </c>
       <c r="E3" s="1"/>
     </row>
     <row r="4" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="4"/>
+      <c r="A4" s="3"/>
       <c r="B4" s="1">
         <v>1000</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="3"/>
+      <c r="D4" s="4"/>
     </row>
     <row r="5" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="4"/>
+      <c r="A5" s="3"/>
       <c r="B5" s="1">
         <v>10000</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D5" s="3"/>
+      <c r="D5" s="4"/>
     </row>
     <row r="6" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="4"/>
+      <c r="A6" s="3"/>
       <c r="B6" s="1">
         <v>20000</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="3"/>
+      <c r="D6" s="4"/>
     </row>
     <row r="7" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="3"/>
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
+      <c r="A7" s="4"/>
+      <c r="B7" s="4"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
       <c r="E7" s="1"/>
     </row>
     <row r="8" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="4" t="s">
+      <c r="A8" s="3" t="s">
         <v>8</v>
       </c>
       <c r="B8" s="1">
@@ -657,53 +540,53 @@
       <c r="C8" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="D8" s="4" t="s">
         <v>12</v>
       </c>
       <c r="E8" s="1"/>
     </row>
     <row r="9" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="4"/>
+      <c r="A9" s="3"/>
       <c r="B9" s="1">
         <v>1000</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D9" s="3"/>
+      <c r="D9" s="4"/>
       <c r="E9" s="1"/>
     </row>
     <row r="10" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="4"/>
+      <c r="A10" s="3"/>
       <c r="B10" s="1">
         <v>10000</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D10" s="3"/>
+      <c r="D10" s="4"/>
       <c r="E10" s="1"/>
     </row>
     <row r="11" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="4"/>
+      <c r="A11" s="3"/>
       <c r="B11" s="1">
         <v>20000</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D11" s="3"/>
+      <c r="D11" s="4"/>
       <c r="E11" s="1"/>
     </row>
     <row r="12" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="3"/>
-      <c r="B12" s="3"/>
-      <c r="C12" s="3"/>
-      <c r="D12" s="3"/>
+      <c r="A12" s="4"/>
+      <c r="B12" s="4"/>
+      <c r="C12" s="4"/>
+      <c r="D12" s="4"/>
       <c r="E12" s="1"/>
     </row>
     <row r="13" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="4" t="s">
+      <c r="A13" s="3" t="s">
         <v>6</v>
       </c>
       <c r="B13" s="1">
@@ -712,53 +595,53 @@
       <c r="C13" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D13" s="4" t="s">
-        <v>14</v>
+      <c r="D13" s="3" t="s">
+        <v>13</v>
       </c>
       <c r="E13" s="1"/>
     </row>
     <row r="14" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="4"/>
+      <c r="A14" s="3"/>
       <c r="B14" s="1">
         <v>1000</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D14" s="4"/>
+      <c r="D14" s="3"/>
       <c r="E14" s="1"/>
     </row>
     <row r="15" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="4"/>
+      <c r="A15" s="3"/>
       <c r="B15" s="1">
         <v>10000</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D15" s="4"/>
+      <c r="D15" s="3"/>
       <c r="E15" s="1"/>
     </row>
     <row r="16" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="4"/>
+      <c r="A16" s="3"/>
       <c r="B16" s="1">
         <v>20000</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D16" s="4"/>
+      <c r="D16" s="3"/>
       <c r="E16" s="1"/>
     </row>
     <row r="17" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="3"/>
-      <c r="B17" s="3"/>
-      <c r="C17" s="3"/>
-      <c r="D17" s="3"/>
+      <c r="A17" s="4"/>
+      <c r="B17" s="4"/>
+      <c r="C17" s="4"/>
+      <c r="D17" s="4"/>
       <c r="E17" s="1"/>
     </row>
     <row r="18" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="4" t="s">
+      <c r="A18" s="3" t="s">
         <v>7</v>
       </c>
       <c r="B18" s="1">
@@ -767,42 +650,42 @@
       <c r="C18" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D18" s="4" t="s">
-        <v>15</v>
+      <c r="D18" s="3" t="s">
+        <v>13</v>
       </c>
       <c r="E18" s="1"/>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A19" s="4"/>
+      <c r="A19" s="3"/>
       <c r="B19" s="1">
         <v>1000</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D19" s="4"/>
+      <c r="D19" s="3"/>
       <c r="E19" s="1"/>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A20" s="4"/>
+      <c r="A20" s="3"/>
       <c r="B20" s="1">
         <v>10000</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D20" s="4"/>
+      <c r="D20" s="3"/>
       <c r="E20" s="1"/>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A21" s="4"/>
+      <c r="A21" s="3"/>
       <c r="B21" s="1">
         <v>20000</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D21" s="4"/>
+      <c r="D21" s="3"/>
       <c r="E21" s="1"/>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.35">
@@ -871,6 +754,5 @@
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>